--- a/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
+++ b/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Fill yellow cells. Product_Owner__c needs the owner's User Id (Data Export: SELECT Id FROM User WHERE Email = '...'). AvailabilityDate as YYYY-MM-DD. BasedOn links the product to the classification so it inherits the attributes.</t>
+          <t>Fill yellow cells. Product_Owner__c needs the owner's User Id (Data Export: SELECT Id FROM User WHERE Email = '...'). AvailabilityDate is a date/time field: enter it as text, e.g. 2026-01-01T00:00:00.000Z (type a leading apostrophe in Excel so it is not reformatted to 01/01/2026). BasedOn links the product to the classification so it inherits the attributes.</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>&lt;YYYY-MM-DD&gt;</t>
+          <t>&lt;YYYY-MM-DDT00:00:00.000Z&gt;</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">

--- a/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
+++ b/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Includes the 12 calculated output attributes (Description starts 'Calculated').</t>
+          <t>Name is prefixed 'AIR ' because AttributeDefinition Name must be unique across the org; Label (shown to users) is unchanged. Includes the 12 calculated output attributes (Description starts 'Calculated').</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
   <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -1518,7 +1518,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>AIR Version</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>AIR Width</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>AIR Length</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Flange Width</t>
+          <t>AIR Flange Width</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Flange Length</t>
+          <t>AIR Flange Length</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>AIR Insulation</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1832,7 +1832,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Louvre</t>
+          <t>AIR Louvre</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1885,7 +1885,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>AIR Controls</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Thermal Release</t>
+          <t>AIR Thermal Release</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Control Bracket Design</t>
+          <t>AIR Control Bracket Design</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2048,7 +2048,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Base Design</t>
+          <t>AIR Base Design</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2101,7 +2101,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Flange Type</t>
+          <t>AIR Flange Type</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2158,7 +2158,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Coating</t>
+          <t>AIR Coating</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>RAL Colour</t>
+          <t>AIR RAL Colour</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2264,7 +2264,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Coating Thickness</t>
+          <t>AIR Coating Thickness</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Installation Type</t>
+          <t>AIR Installation Type</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Mounting Angle</t>
+          <t>AIR Mounting Angle</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Wind Baffle</t>
+          <t>AIR Wind Baffle</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>AIR Delivery</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2533,7 +2533,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Snow Load</t>
+          <t>AIR Snow Load</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Wind Load</t>
+          <t>AIR Wind Load</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Ambient Air Temperature</t>
+          <t>AIR Ambient Air Temperature</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2688,7 +2688,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Pressure Day to Day</t>
+          <t>AIR Pressure Day to Day</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Pressure Smoke Ventilation</t>
+          <t>AIR Pressure Smoke Ventilation</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Cylinder</t>
+          <t>AIR Cylinder</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CO2 Bottle</t>
+          <t>AIR CO2 Bottle</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2892,7 +2892,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Pressure Standby Reservoir</t>
+          <t>AIR Pressure Standby Reservoir</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Electric Drive</t>
+          <t>AIR Electric Drive</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Wind Suction Load WL</t>
+          <t>AIR Wind Suction Load WL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3039,7 +3039,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Geometric Area Av</t>
+          <t>AIR Geometric Area Av</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3088,7 +3088,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Aerodynamic Area Aa</t>
+          <t>AIR Aerodynamic Area Aa</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>U-Value</t>
+          <t>AIR U-Value</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3186,7 +3186,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Louvre Weight</t>
+          <t>AIR Louvre Weight</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Total Weight</t>
+          <t>AIR Total Weight</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3284,7 +3284,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max SL Pneumatic Cylinder</t>
+          <t>AIR Max SL Pneumatic Cylinder</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3333,7 +3333,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max SL Motor</t>
+          <t>AIR Max SL Motor</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">

--- a/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
+++ b/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Several categories may already exist from ECO (Device_Configuration, Filling, Control_and_Drive, Base_and_Flange, Options, Finish, Calculated_Outputs). A DUPLICATE_VALUE error on those rows is fine – they are reused.</t>
+          <t>Several categories may already exist from earlier products, e.g. ECO (Device_Configuration, Filling, Control_and_Drive, Base_and_Flange, Options, Finish, Calculated_Outputs). A DUPLICATE_VALUE error on those rows is fine – they are reused.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Fill yellow cells. Product_Owner__c needs the owner's User Id (Data Export: SELECT Id FROM User WHERE Email = '...'). AvailabilityDate is a date/time field: enter it as text, e.g. 2026-01-01T00:00:00.000Z (type a leading apostrophe in Excel so it is not reformatted to 01/01/2026). BasedOn links the product to the classification so it inherits the attributes.</t>
+          <t>Fill yellow cells. Product_Owner__c needs the owner's User Id starting 005, not an alias or e-mail (Data Export: SELECT Id FROM User WHERE Email = '...'). AvailabilityDate is a date/time field: enter it as text, e.g. 2026-01-01T00:00:00.000Z (type a leading apostrophe in Excel so it is not reformatted to 01/01/2026). BasedOn links the product to the classification so it inherits the attributes.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ProductId = the Id Inspector returns in step 06. ProductCategoryId: Data Export SELECT Id, Name FROM ProductCategory WHERE Name = 'Natural Ventilation'.</t>
+          <t>ProductId = the Id Inspector returns in step 06. ProductCategoryId: Data Export SELECT Id, Name FROM ProductCategory WHERE Name = '&lt;category from the Product sheet&gt;'.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -747,7 +747,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>&lt;Id of Natural Ventilation&gt;</t>
+          <t>&lt;ProductCategory Id&gt;</t>
         </is>
       </c>
     </row>

--- a/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
+++ b/OneDrive_2026-09-29/Claude RCA Product/09-airlite-product-template/Airlite_RCA_Import_Inspector.xlsx
@@ -450,13 +450,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Data Export query to find the Ids for this step</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -496,6 +502,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -516,6 +523,7 @@
           <t>Name is prefixed 'AIR ' because AttributeDefinition Name must be unique across the org; Label (shown to users) is unchanged. Includes the 12 calculated output attributes (Description starts 'Calculated').</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -536,6 +544,7 @@
           <t>Code is prefixed (AIR_&lt;Picklist&gt;_&lt;Value&gt;) so it can't clash with ECO codes already in the org; Value is unchanged.</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -556,6 +565,7 @@
           <t>Several categories may already exist from earlier products, e.g. ECO (Device_Configuration, Filling, Control_and_Drive, Base_and_Flange, Options, Finish, Calculated_Outputs). A DUPLICATE_VALUE error on those rows is fine – they are reused.</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -572,6 +582,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -589,7 +600,15 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Fill yellow cells. Product_Owner__c needs the owner's User Id starting 005, not an alias or e-mail (Data Export: SELECT Id FROM User WHERE Email = '...'). AvailabilityDate is a date/time field: enter it as text, e.g. 2026-01-01T00:00:00.000Z (type a leading apostrophe in Excel so it is not reformatted to 01/01/2026). BasedOn links the product to the classification so it inherits the attributes.</t>
+          <t>Fill yellow cells. Product_Owner__c = owner's User Id (starts 005, not alias/e-mail). AvailabilityDate is a date/time: type 2026-01-01T00:00:00.000Z exactly, NO apostrophe (cells are Text). Product_Family_ROD__c optional – use an existing value. BasedOn links the product to the classification so it inherits the attributes.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Product owner User Id (005…):
+SELECT Id, Name, Alias, Email FROM User WHERE Alias = '&lt;alias&gt;' OR Email = '&lt;e-mail&gt;'
+Existing product family values:
+SELECT Product_Family_ROD__c, COUNT(Id) FROM Product2 WHERE Product_Family_ROD__c != null GROUP BY Product_Family_ROD__c</t>
         </is>
       </c>
     </row>
@@ -608,6 +627,12 @@
         <v>36</v>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Check all attributes from step 02 exist:
+SELECT Code, Name, DataType FROM AttributeDefinition WHERE Code LIKE 'AIR_%' ORDER BY Code</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -628,6 +653,7 @@
           <t>Calculated outputs are IsReadOnly = true. DisplayType is only set (Dropdown) for picklists.</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -645,7 +671,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ProductId = the Id Inspector returns in step 06. ProductCategoryId: Data Export SELECT Id, Name FROM ProductCategory WHERE Name = '&lt;category from the Product sheet&gt;'.</t>
+          <t>Object = ProductCategoryProduct (Inspector keeps the last object selected – change it!). Both columns need record Ids (01t… / 0ZG…), not names – see the Data Export queries on the Import Steps tab.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ProductId (01t…) – the product from step 06:
+SELECT Id, Name, ProductCode FROM Product2 WHERE ProductCode = 'AIR'
+ProductCategoryId (0ZG…) with its catalog:
+SELECT Id, Name, Catalog.Name, CatalogId FROM ProductCategory WHERE Name LIKE '%&lt;category&gt;%' ORDER BY Catalog.Name, Name
+Which category/catalog a similar product uses:
+SELECT ProductCategoryId, ProductCategory.Name, ProductCategory.Catalog.Name FROM ProductCategoryProduct WHERE Product.ProductCode = '&lt;similar product code&gt;'</t>
         </is>
       </c>
     </row>
@@ -668,6 +704,12 @@
           <t>Skip until the factory supplies prices. Standard Price Book entry first, then the KLAW price book.</t>
         </is>
       </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Pricebook2Id:
+SELECT Id, Name, IsStandard FROM Pricebook2 WHERE IsActive = true</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -688,12 +730,14 @@
           <t>Skip until prices are known (see the template's Configurable Product Pricing tab).</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -708,6 +752,7 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
